--- a/release/templates/combo_template_all_characters_full.xlsx
+++ b/release/templates/combo_template_all_characters_full.xlsx
@@ -8,41 +8,44 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Edit\Documents\SF6_Lab\release\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8A988-0643-4C99-A0ED-B30176997B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9759BAA3-F870-401B-94E3-02968561564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" firstSheet="8" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aki" sheetId="1" r:id="rId1"/>
     <sheet name="alex" sheetId="2" r:id="rId2"/>
-    <sheet name="blanka" sheetId="3" r:id="rId3"/>
-    <sheet name="cammy" sheetId="4" r:id="rId4"/>
-    <sheet name="chunli" sheetId="5" r:id="rId5"/>
-    <sheet name="cviper" sheetId="6" r:id="rId6"/>
-    <sheet name="deejay" sheetId="7" r:id="rId7"/>
-    <sheet name="dhalsim" sheetId="8" r:id="rId8"/>
-    <sheet name="ed" sheetId="9" r:id="rId9"/>
-    <sheet name="ehonda" sheetId="10" r:id="rId10"/>
-    <sheet name="elena" sheetId="11" r:id="rId11"/>
-    <sheet name="gouki_akuma" sheetId="12" r:id="rId12"/>
-    <sheet name="guile" sheetId="13" r:id="rId13"/>
-    <sheet name="Ingrid" sheetId="30" r:id="rId14"/>
-    <sheet name="jamie" sheetId="14" r:id="rId15"/>
-    <sheet name="jp" sheetId="15" r:id="rId16"/>
-    <sheet name="juri" sheetId="16" r:id="rId17"/>
-    <sheet name="ken" sheetId="17" r:id="rId18"/>
-    <sheet name="kimberly" sheetId="18" r:id="rId19"/>
-    <sheet name="lily" sheetId="19" r:id="rId20"/>
-    <sheet name="luke" sheetId="20" r:id="rId21"/>
-    <sheet name="mai" sheetId="21" r:id="rId22"/>
-    <sheet name="manon" sheetId="22" r:id="rId23"/>
-    <sheet name="marisa" sheetId="23" r:id="rId24"/>
-    <sheet name="rashid" sheetId="24" r:id="rId25"/>
-    <sheet name="ryu" sheetId="25" r:id="rId26"/>
-    <sheet name="sagat" sheetId="26" r:id="rId27"/>
-    <sheet name="terry" sheetId="27" r:id="rId28"/>
-    <sheet name="vega_mbison" sheetId="28" r:id="rId29"/>
-    <sheet name="zangief" sheetId="29" r:id="rId30"/>
+    <sheet name="arjun" sheetId="32" r:id="rId3"/>
+    <sheet name="blanka" sheetId="3" r:id="rId4"/>
+    <sheet name="cammy" sheetId="4" r:id="rId5"/>
+    <sheet name="chunli" sheetId="5" r:id="rId6"/>
+    <sheet name="cviper" sheetId="6" r:id="rId7"/>
+    <sheet name="deejay" sheetId="7" r:id="rId8"/>
+    <sheet name="dhalsim" sheetId="8" r:id="rId9"/>
+    <sheet name="ed" sheetId="9" r:id="rId10"/>
+    <sheet name="ehonda" sheetId="10" r:id="rId11"/>
+    <sheet name="elena" sheetId="11" r:id="rId12"/>
+    <sheet name="gouki_akuma" sheetId="12" r:id="rId13"/>
+    <sheet name="guile" sheetId="13" r:id="rId14"/>
+    <sheet name="ingrid" sheetId="30" r:id="rId15"/>
+    <sheet name="jamie" sheetId="14" r:id="rId16"/>
+    <sheet name="jp" sheetId="15" r:id="rId17"/>
+    <sheet name="juri" sheetId="16" r:id="rId18"/>
+    <sheet name="ken" sheetId="17" r:id="rId19"/>
+    <sheet name="kimberly" sheetId="18" r:id="rId20"/>
+    <sheet name="lily" sheetId="19" r:id="rId21"/>
+    <sheet name="luke" sheetId="20" r:id="rId22"/>
+    <sheet name="mai" sheetId="21" r:id="rId23"/>
+    <sheet name="manon" sheetId="22" r:id="rId24"/>
+    <sheet name="marisa" sheetId="23" r:id="rId25"/>
+    <sheet name="rashid" sheetId="24" r:id="rId26"/>
+    <sheet name="ryu" sheetId="25" r:id="rId27"/>
+    <sheet name="sagat" sheetId="26" r:id="rId28"/>
+    <sheet name="terry" sheetId="27" r:id="rId29"/>
+    <sheet name="vega_mbison" sheetId="28" r:id="rId30"/>
+    <sheet name="yasmine" sheetId="34" r:id="rId31"/>
+    <sheet name="zangief" sheetId="29" r:id="rId32"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId33"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -54,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="53">
   <si>
     <t>Combo</t>
   </si>
@@ -313,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -325,11 +328,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -709,65 +714,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -1224,7 +1229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1234,65 +1239,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -1749,7 +1754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1759,65 +1764,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -2274,7 +2279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2284,65 +2289,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -2799,7 +2804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2809,65 +2814,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -3324,7 +3329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9D0E28-B64D-4C6E-8BE3-BF7B3056C062}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3334,65 +3339,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -3835,21 +3840,21 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AO1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9D0E28-B64D-4C6E-8BE3-BF7B3056C062}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3859,65 +3864,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -4360,21 +4365,21 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AO1"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AC1:AD1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4384,65 +4389,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -4899,7 +4904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4909,65 +4914,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -5424,7 +5429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5434,65 +5439,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -5949,7 +5954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5959,65 +5964,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -6484,65 +6489,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -6999,7 +7004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7009,65 +7014,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -7524,7 +7529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7534,65 +7539,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -8049,7 +8054,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8059,65 +8064,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -8574,7 +8579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8584,65 +8589,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -9099,7 +9104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9109,65 +9114,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -9624,7 +9629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9634,65 +9639,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -10149,7 +10154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10159,65 +10164,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -10674,7 +10679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10684,65 +10689,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -11199,7 +11204,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11209,65 +11214,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -11724,7 +11729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11734,65 +11739,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -12249,76 +12254,77 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08347A5-00F6-4622-B3C6-9959EB4062BA}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
-    <col min="2" max="2" width="46.7265625" customWidth="1"/>
-    <col min="3" max="34" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" style="4" customWidth="1"/>
+    <col min="3" max="34" width="12.7265625" style="4" customWidth="1"/>
+    <col min="35" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
-      <c r="AE1" t="s">
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" t="s">
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -12425,28 +12431,28 @@
       <c r="AH2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -12760,21 +12766,21 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AO1"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AC1:AD1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -12784,65 +12790,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -13298,77 +13304,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{524E164F-14D8-46CC-B994-20E76E0CD62A}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
-    <col min="2" max="2" width="46.7265625" customWidth="1"/>
-    <col min="3" max="34" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" style="5" customWidth="1"/>
+    <col min="3" max="34" width="12.7265625" style="5" customWidth="1"/>
+    <col min="35" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
-      <c r="AE1" t="s">
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" t="s">
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -13475,28 +13482,28 @@
       <c r="AH2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -13810,21 +13817,21 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AO1"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:Y1"/>
     <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AC1:AD1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -13834,65 +13841,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -14348,8 +14355,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DF7C44-82A5-4F19-B7F5-FF38619C3FF2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -14359,65 +14375,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -14873,8 +14889,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -14884,65 +14900,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -15398,8 +15414,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -15409,65 +15425,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -15923,8 +15939,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AP10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -15934,65 +15950,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="4" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4" t="s">
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="4"/>
+      <c r="AD1" s="6"/>
       <c r="AE1" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="5" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="4" t="s">
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
       <c r="AP1" t="s">
         <v>9</v>
       </c>
@@ -16446,4 +16462,1054 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:AP10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
+    <col min="3" max="34" width="12.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="6"/>
+      <c r="AE1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AK1:AO1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="L1:Y1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AC1:AD1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:AP10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" customWidth="1"/>
+    <col min="3" max="34" width="12.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="6"/>
+      <c r="AE1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AK1:AO1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="L1:Y1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AC1:AD1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>